--- a/tracking_forms/020_ai_inventory_tracking_pilot_application--tracking_forms.xlsx
+++ b/tracking_forms/020_ai_inventory_tracking_pilot_application--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -998,12 +998,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'manufacturing',_'value':_'manufacturing'}</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Manufacturing', 'value': 'manufacturing'}</t>
+          <t>Manufacturing</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'warehousing_&amp;_distribution',_'value':_'warehousing'}</t>
+          <t>warehousing_&amp;_distribution</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Warehousing &amp; Distribution', 'value': 'warehousing'}</t>
+          <t>Warehousing &amp; Distribution</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'retail_/_consumer_goods',_'value':_'retail'}</t>
+          <t>retail_/_consumer_goods</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Retail / Consumer Goods', 'value': 'retail'}</t>
+          <t>Retail / Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'healthcare_/_medical_supplies',_'value':_'healthcare'}</t>
+          <t>healthcare_/_medical_supplies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Healthcare / Medical Supplies', 'value': 'healthcare'}</t>
+          <t>Healthcare / Medical Supplies</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'e-commerce',_'value':_'ecommerce'}</t>
+          <t>e-commerce</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'E-commerce', 'value': 'ecommerce'}</t>
+          <t>E-commerce</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'under_1,000',_'value':_'under_1k'}</t>
+          <t>under_1,000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Under 1,000', 'value': 'under_1k'}</t>
+          <t>Under 1,000</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'1,000_-_10,000',_'value':_'1k_10k'}</t>
+          <t>1,000_-_10,000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '1,000 - 10,000', 'value': '1k_10k'}</t>
+          <t>1,000 - 10,000</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'10,001_-_50,000',_'value':_'10k_50k'}</t>
+          <t>10,001_-_50,000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '10,001 - 50,000', 'value': '10k_50k'}</t>
+          <t>10,001 - 50,000</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'over_50,000',_'value':_'over_50k'}</t>
+          <t>over_50,000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Over 50,000', 'value': 'over_50k'}</t>
+          <t>Over 50,000</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'manual_(paper/whiteboard)',_'value':_'manual'}</t>
+          <t>manual_(paper/whiteboard)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Manual (Paper/Whiteboard)', 'value': 'manual'}</t>
+          <t>Manual (Paper/Whiteboard)</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'spreadsheets_(excel_/_google_sheets)',_'value':_'spreadsheets'}</t>
+          <t>spreadsheets_(excel_/_google_sheets)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Spreadsheets (Excel / Google Sheets)', 'value': 'spreadsheets'}</t>
+          <t>Spreadsheets (Excel / Google Sheets)</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'dedicated_inventory_software',_'value':_'dedicated_sw'}</t>
+          <t>dedicated_inventory_software</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Dedicated Inventory Software', 'value': 'dedicated_sw'}</t>
+          <t>Dedicated Inventory Software</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'enterprise_resource_planning_(erp)',_'value':_'erp'}</t>
+          <t>enterprise_resource_planning_(erp)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Enterprise Resource Planning (ERP)', 'value': 'erp'}</t>
+          <t>Enterprise Resource Planning (ERP)</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'low_inventory_accuracy',_'value':_'accuracy'}</t>
+          <t>low_inventory_accuracy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Low Inventory Accuracy', 'value': 'accuracy'}</t>
+          <t>Low Inventory Accuracy</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'frequent_stockouts_/_overstocks',_'value':_'stock_balance'}</t>
+          <t>frequent_stockouts_/_overstocks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Frequent Stockouts / Overstocks', 'value': 'stock_balance'}</t>
+          <t>Frequent Stockouts / Overstocks</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'inaccurate_demand_forecasting',_'value':_'forecasting'}</t>
+          <t>inaccurate_demand_forecasting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Inaccurate Demand Forecasting', 'value': 'forecasting'}</t>
+          <t>Inaccurate Demand Forecasting</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'time-consuming_manual_audits',_'value':_'manual_audits'}</t>
+          <t>time-consuming_manual_audits</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Time-consuming Manual Audits', 'value': 'manual_audits'}</t>
+          <t>Time-consuming Manual Audits</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'poor_visibility_across_multiple_sites',_'value':_'visibility'}</t>
+          <t>poor_visibility_across_multiple_sites</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Poor Visibility Across Multiple Sites', 'value': 'visibility'}</t>
+          <t>Poor Visibility Across Multiple Sites</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'predictive_demand_forecasting',_'value':_'predictive_demand'}</t>
+          <t>predictive_demand_forecasting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Predictive Demand Forecasting', 'value': 'predictive_demand'}</t>
+          <t>Predictive Demand Forecasting</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'computer_vision_for_visual_counting',_'value':_'computer_vision'}</t>
+          <t>computer_vision_for_visual_counting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Computer Vision for Visual Counting', 'value': 'computer_vision'}</t>
+          <t>Computer Vision for Visual Counting</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'anomaly_detection_(theft/damage/loss)',_'value':_'anomaly_detection'}</t>
+          <t>anomaly_detection_(theft/damage/loss)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Anomaly Detection (Theft/Damage/Loss)', 'value': 'anomaly_detection'}</t>
+          <t>Anomaly Detection (Theft/Damage/Loss)</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'automated_reorder_optimization',_'value':_'reorder_opt'}</t>
+          <t>automated_reorder_optimization</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Automated Reorder Optimization', 'value': 'reorder_opt'}</t>
+          <t>Automated Reorder Optimization</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'warehouse_slotting_optimization',_'value':_'slotting'}</t>
+          <t>warehouse_slotting_optimization</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Warehouse Slotting Optimization', 'value': 'slotting'}</t>
+          <t>Warehouse Slotting Optimization</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'high_readiness_(reliable_fiber/cloud_integrated)',_'value':_'high'}</t>
+          <t>high_readiness_(reliable_fiber/cloud_integrated)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'High Readiness (Reliable Fiber/Cloud Integrated)', 'value': 'high'}</t>
+          <t>High Readiness (Reliable Fiber/Cloud Integrated)</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'moderate_readiness_(standard_internet/willing_to_upgrade)',_'value':_'moderate'}</t>
+          <t>moderate_readiness_(standard_internet/willing_to_upgrade)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate Readiness (Standard Internet/Willing to upgrade)', 'value': 'moderate'}</t>
+          <t>Moderate Readiness (Standard Internet/Willing to upgrade)</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'low_readiness_(spotty_connection/legacy_hardware)',_'value':_'low'}</t>
+          <t>low_readiness_(spotty_connection/legacy_hardware)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Low Readiness (Spotty connection/Legacy hardware)', 'value': 'low'}</t>
+          <t>Low Readiness (Spotty connection/Legacy hardware)</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_structured_and_digital',_'value':_'yes_structured'}</t>
+          <t>yes,_structured_and_digital</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, structured and digital', 'value': 'yes_structured'}</t>
+          <t>Yes, structured and digital</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_but_needs_cleaning',_'value':_'yes_unstructured'}</t>
+          <t>yes,_but_needs_cleaning</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, but needs cleaning', 'value': 'yes_unstructured'}</t>
+          <t>Yes, but needs cleaning</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'budget_approved_for_pilot',_'value':_'approved'}</t>
+          <t>budget_approved_for_pilot</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Budget Approved for Pilot', 'value': 'approved'}</t>
+          <t>Budget Approved for Pilot</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'seeking_approval_/_research_phase',_'value':_'seeking'}</t>
+          <t>seeking_approval_/_research_phase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Seeking Approval / Research phase', 'value': 'seeking'}</t>
+          <t>Seeking Approval / Research phase</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'requesting_fully_funded_pilot_(grant)',_'value':_'grant'}</t>
+          <t>requesting_fully_funded_pilot_(grant)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Requesting Fully Funded Pilot (Grant)', 'value': 'grant'}</t>
+          <t>Requesting Fully Funded Pilot (Grant)</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'no_/_need_legal_review',_'value':_'legal_review'}</t>
+          <t>no_/_need_legal_review</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'No / Need Legal Review', 'value': 'legal_review'}</t>
+          <t>No / Need Legal Review</t>
         </is>
       </c>
     </row>
